--- a/Student Attendance/Class 1/Class 1 - Monthly Attendance - August-2024.xlsx
+++ b/Student Attendance/Class 1/Class 1 - Monthly Attendance - August-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\Class 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4643527D-5FDB-4F8A-A302-FF02CB71B983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BD4BE0-CAD6-480A-8D20-9FC03B7E3C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="542" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="542" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class-I (Girls)" sheetId="4" r:id="rId1"/>
@@ -671,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -719,21 +719,30 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -742,19 +751,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
@@ -764,46 +761,9 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -841,6 +801,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -889,14 +856,44 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1210,75 +1207,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
     </row>
     <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1349,25 +1346,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W3" s="33" t="s">
+      <c r="W3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="33" t="s">
+      <c r="X3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="27"/>
+      <c r="Z3" s="29"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
     <row r="4" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="21">
         <v>45519</v>
       </c>
@@ -1419,8 +1416,8 @@
       <c r="V4" s="21">
         <v>45535</v>
       </c>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
       <c r="Y4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1453,13 +1450,13 @@
       <c r="H5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="24" t="s">
         <v>131</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="25" t="s">
         <v>129</v>
       </c>
       <c r="L5" s="11" t="s">
@@ -1471,13 +1468,13 @@
       <c r="N5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="30" t="s">
+      <c r="O5" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="P5" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" s="30" t="s">
+      <c r="Q5" s="25" t="s">
         <v>133</v>
       </c>
       <c r="R5" s="11" t="s">
@@ -1489,18 +1486,18 @@
       <c r="T5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U5" s="30" t="s">
+      <c r="U5" s="25" t="s">
         <v>130</v>
       </c>
       <c r="V5" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W5" s="5">
-        <f>COUNTIF(F5:V5,"P")</f>
+        <f t="shared" ref="W5:W28" si="1">COUNTIF(F5:V5,"P")</f>
         <v>9</v>
       </c>
       <c r="X5" s="5">
-        <f>COUNTIF(F5:V5,"A")</f>
+        <f t="shared" ref="X5:X28" si="2">COUNTIF(F5:V5,"A")</f>
         <v>2</v>
       </c>
       <c r="Y5" s="5" t="s">
@@ -1537,11 +1534,11 @@
       <c r="H6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="34"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="31"/>
+      <c r="K6" s="26"/>
       <c r="L6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1551,9 +1548,9 @@
       <c r="N6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="31"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="31"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="26"/>
       <c r="R6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1563,16 +1560,16 @@
       <c r="T6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U6" s="31"/>
+      <c r="U6" s="26"/>
       <c r="V6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W6" s="5">
-        <f>COUNTIF(F6:V6,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X6" s="5">
-        <f>COUNTIF(F6:V6,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="Y6" s="5" t="s">
@@ -1607,11 +1604,11 @@
       <c r="H7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="34"/>
+      <c r="I7" s="24"/>
       <c r="J7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="26"/>
       <c r="L7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1621,9 +1618,9 @@
       <c r="N7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="31"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="26"/>
       <c r="R7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1633,16 +1630,16 @@
       <c r="T7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="31"/>
+      <c r="U7" s="26"/>
       <c r="V7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W7" s="5">
-        <f>COUNTIF(F7:V7,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X7" s="5">
-        <f>COUNTIF(F7:V7,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Y7" s="3"/>
@@ -1671,11 +1668,11 @@
       <c r="H8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="34"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="26"/>
       <c r="L8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1685,9 +1682,9 @@
       <c r="N8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="31"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="26"/>
       <c r="R8" s="11" t="s">
         <v>28</v>
       </c>
@@ -1697,24 +1694,24 @@
       <c r="T8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="31"/>
+      <c r="U8" s="26"/>
       <c r="V8" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W8" s="5">
-        <f>COUNTIF(F8:V8,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X8" s="5">
-        <f>COUNTIF(F8:V8,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="Y8" s="25" t="s">
+      <c r="Y8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="26"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1739,11 +1736,11 @@
       <c r="H9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="34"/>
+      <c r="I9" s="24"/>
       <c r="J9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="26"/>
       <c r="L9" s="11" t="s">
         <v>29</v>
       </c>
@@ -1753,9 +1750,9 @@
       <c r="N9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="31"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="31"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="26"/>
       <c r="R9" s="11" t="s">
         <v>28</v>
       </c>
@@ -1765,16 +1762,16 @@
       <c r="T9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U9" s="31"/>
+      <c r="U9" s="26"/>
       <c r="V9" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W9" s="5">
-        <f>COUNTIF(F9:V9,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X9" s="5">
-        <f>COUNTIF(F9:V9,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Y9" s="5" t="s">
@@ -1813,11 +1810,11 @@
       <c r="H10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="34"/>
+      <c r="I10" s="24"/>
       <c r="J10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="31"/>
+      <c r="K10" s="26"/>
       <c r="L10" s="11" t="s">
         <v>29</v>
       </c>
@@ -1827,9 +1824,9 @@
       <c r="N10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="31"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="26"/>
       <c r="R10" s="11" t="s">
         <v>28</v>
       </c>
@@ -1839,16 +1836,16 @@
       <c r="T10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U10" s="31"/>
+      <c r="U10" s="26"/>
       <c r="V10" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W10" s="5">
-        <f>COUNTIF(F10:V10,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X10" s="5">
-        <f>COUNTIF(F10:V10,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="Y10" s="5" t="s">
@@ -1890,11 +1887,11 @@
       <c r="H11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="34"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="31"/>
+      <c r="K11" s="26"/>
       <c r="L11" s="11" t="s">
         <v>29</v>
       </c>
@@ -1904,9 +1901,9 @@
       <c r="N11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="31"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="31"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="26"/>
       <c r="R11" s="11" t="s">
         <v>28</v>
       </c>
@@ -1916,16 +1913,16 @@
       <c r="T11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U11" s="31"/>
+      <c r="U11" s="26"/>
       <c r="V11" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W11" s="5">
-        <f>COUNTIF(F11:V11,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X11" s="5">
-        <f>COUNTIF(F11:V11,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y11" s="5" t="s">
@@ -1967,11 +1964,11 @@
       <c r="H12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="34"/>
+      <c r="I12" s="24"/>
       <c r="J12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="26"/>
       <c r="L12" s="11" t="s">
         <v>29</v>
       </c>
@@ -1981,9 +1978,9 @@
       <c r="N12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="31"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="31"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="26"/>
       <c r="R12" s="11" t="s">
         <v>29</v>
       </c>
@@ -1993,16 +1990,16 @@
       <c r="T12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="31"/>
+      <c r="U12" s="26"/>
       <c r="V12" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W12" s="5">
-        <f>COUNTIF(F12:V12,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X12" s="5">
-        <f>COUNTIF(F12:V12,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y12" s="5" t="s">
@@ -2044,11 +2041,11 @@
       <c r="H13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="34"/>
+      <c r="I13" s="24"/>
       <c r="J13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="31"/>
+      <c r="K13" s="26"/>
       <c r="L13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2058,9 +2055,9 @@
       <c r="N13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="31"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="26"/>
       <c r="R13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2070,16 +2067,16 @@
       <c r="T13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U13" s="31"/>
+      <c r="U13" s="26"/>
       <c r="V13" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W13" s="5">
-        <f>COUNTIF(F13:V13,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X13" s="5">
-        <f>COUNTIF(F13:V13,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y13" s="3"/>
@@ -2110,11 +2107,11 @@
       <c r="H14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="34"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="31"/>
+      <c r="K14" s="26"/>
       <c r="L14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2124,9 +2121,9 @@
       <c r="N14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="31"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="31"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="26"/>
       <c r="R14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2136,16 +2133,16 @@
       <c r="T14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U14" s="31"/>
+      <c r="U14" s="26"/>
       <c r="V14" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W14" s="5">
-        <f>COUNTIF(F14:V14,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="X14" s="5">
-        <f>COUNTIF(F14:V14,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y14" s="19"/>
@@ -2176,11 +2173,11 @@
       <c r="H15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="34"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="31"/>
+      <c r="K15" s="26"/>
       <c r="L15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2190,9 +2187,9 @@
       <c r="N15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="31"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="26"/>
       <c r="R15" s="11" t="s">
         <v>28</v>
       </c>
@@ -2202,16 +2199,16 @@
       <c r="T15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U15" s="31"/>
+      <c r="U15" s="26"/>
       <c r="V15" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W15" s="5">
-        <f>COUNTIF(F15:V15,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X15" s="5">
-        <f>COUNTIF(F15:V15,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Y15" s="3"/>
@@ -2242,11 +2239,11 @@
       <c r="H16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="34"/>
+      <c r="I16" s="24"/>
       <c r="J16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="26"/>
       <c r="L16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2256,9 +2253,9 @@
       <c r="N16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="O16" s="31"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="31"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="26"/>
       <c r="R16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2268,24 +2265,24 @@
       <c r="T16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U16" s="31"/>
+      <c r="U16" s="26"/>
       <c r="V16" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W16" s="5">
-        <f>COUNTIF(F16:V16,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X16" s="5">
-        <f>COUNTIF(F16:V16,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="Y16" s="25" t="s">
+      <c r="Y16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="26"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="30"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2310,11 +2307,11 @@
       <c r="H17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="34"/>
+      <c r="I17" s="24"/>
       <c r="J17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="26"/>
       <c r="L17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2324,9 +2321,9 @@
       <c r="N17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="31"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="31"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="26"/>
       <c r="R17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2336,16 +2333,16 @@
       <c r="T17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U17" s="31"/>
+      <c r="U17" s="26"/>
       <c r="V17" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W17" s="5">
-        <f>COUNTIF(F17:V17,"P")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="X17" s="5">
-        <f>COUNTIF(F17:V17,"A")</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="Y17" s="5" t="s">
@@ -2378,9 +2375,9 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
-      <c r="I18" s="34"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="11"/>
-      <c r="K18" s="31"/>
+      <c r="K18" s="26"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11" t="s">
         <v>29</v>
@@ -2388,9 +2385,9 @@
       <c r="N18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="31"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="31"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="26"/>
       <c r="R18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2400,16 +2397,16 @@
       <c r="T18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U18" s="31"/>
+      <c r="U18" s="26"/>
       <c r="V18" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W18" s="5">
-        <f>COUNTIF(F18:V18,"P")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="X18" s="5">
-        <f>COUNTIF(F18:V18,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y18" s="5" t="s">
@@ -2445,17 +2442,17 @@
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="34"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="11"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="26"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="31"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="31"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="26"/>
       <c r="R19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2465,16 +2462,16 @@
       <c r="T19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U19" s="31"/>
+      <c r="U19" s="26"/>
       <c r="V19" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W19" s="5">
-        <f>COUNTIF(F19:V19,"P")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="X19" s="5">
-        <f>COUNTIF(F19:V19,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y19" s="5" t="s">
@@ -2516,11 +2513,11 @@
       <c r="H20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="34"/>
+      <c r="I20" s="24"/>
       <c r="J20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="26"/>
       <c r="L20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2530,9 +2527,9 @@
       <c r="N20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="31"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="31"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="26"/>
       <c r="R20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2542,16 +2539,16 @@
       <c r="T20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U20" s="31"/>
+      <c r="U20" s="26"/>
       <c r="V20" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W20" s="5">
-        <f>COUNTIF(F20:V20,"P")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="X20" s="5">
-        <f>COUNTIF(F20:V20,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Y20" s="5" t="s">
@@ -2587,17 +2584,17 @@
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="34"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="31"/>
+      <c r="K21" s="26"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="31"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="31"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="26"/>
       <c r="R21" s="11" t="s">
         <v>28</v>
       </c>
@@ -2607,16 +2604,16 @@
       <c r="T21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U21" s="31"/>
+      <c r="U21" s="26"/>
       <c r="V21" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W21" s="5">
-        <f>COUNTIF(F21:V21,"P")</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="X21" s="5">
-        <f>COUNTIF(F21:V21,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2637,17 +2634,17 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="34"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="31"/>
+      <c r="K22" s="26"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
       <c r="N22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="31"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="31"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="26"/>
       <c r="R22" s="11" t="s">
         <v>28</v>
       </c>
@@ -2657,16 +2654,16 @@
       <c r="T22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U22" s="31"/>
+      <c r="U22" s="26"/>
       <c r="V22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W22" s="5">
-        <f>COUNTIF(F22:V22,"P")</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="X22" s="5">
-        <f>COUNTIF(F22:V22,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2693,11 +2690,11 @@
       <c r="H23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="34"/>
+      <c r="I23" s="24"/>
       <c r="J23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="31"/>
+      <c r="K23" s="26"/>
       <c r="L23" s="11" t="s">
         <v>29</v>
       </c>
@@ -2707,9 +2704,9 @@
       <c r="N23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="31"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="31"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="26"/>
       <c r="R23" s="11" t="s">
         <v>29</v>
       </c>
@@ -2719,16 +2716,16 @@
       <c r="T23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U23" s="31"/>
+      <c r="U23" s="26"/>
       <c r="V23" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W23" s="5">
-        <f>COUNTIF(F23:V23,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X23" s="5">
-        <f>COUNTIF(F23:V23,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -2755,11 +2752,11 @@
       <c r="H24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="34"/>
+      <c r="I24" s="24"/>
       <c r="J24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="26"/>
       <c r="L24" s="11" t="s">
         <v>29</v>
       </c>
@@ -2769,9 +2766,9 @@
       <c r="N24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="31"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="31"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="26"/>
       <c r="R24" s="11" t="s">
         <v>29</v>
       </c>
@@ -2781,16 +2778,16 @@
       <c r="T24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U24" s="31"/>
+      <c r="U24" s="26"/>
       <c r="V24" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W24" s="5">
-        <f>COUNTIF(F24:V24,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X24" s="5">
-        <f>COUNTIF(F24:V24,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2817,11 +2814,11 @@
       <c r="H25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="34"/>
+      <c r="I25" s="24"/>
       <c r="J25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="26"/>
       <c r="L25" s="11" t="s">
         <v>29</v>
       </c>
@@ -2831,9 +2828,9 @@
       <c r="N25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O25" s="31"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="31"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="26"/>
       <c r="R25" s="11" t="s">
         <v>29</v>
       </c>
@@ -2843,16 +2840,16 @@
       <c r="T25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U25" s="31"/>
+      <c r="U25" s="26"/>
       <c r="V25" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W25" s="5">
-        <f>COUNTIF(F25:V25,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X25" s="5">
-        <f>COUNTIF(F25:V25,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2879,11 +2876,11 @@
       <c r="H26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="34"/>
+      <c r="I26" s="24"/>
       <c r="J26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K26" s="31"/>
+      <c r="K26" s="26"/>
       <c r="L26" s="11" t="s">
         <v>28</v>
       </c>
@@ -2893,9 +2890,9 @@
       <c r="N26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O26" s="31"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="31"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="26"/>
       <c r="R26" s="11" t="s">
         <v>29</v>
       </c>
@@ -2905,16 +2902,16 @@
       <c r="T26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U26" s="31"/>
+      <c r="U26" s="26"/>
       <c r="V26" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W26" s="5">
-        <f>COUNTIF(F26:V26,"P")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="X26" s="5">
-        <f>COUNTIF(F26:V26,"A")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -2941,11 +2938,11 @@
       <c r="H27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="34"/>
+      <c r="I27" s="24"/>
       <c r="J27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="31"/>
+      <c r="K27" s="26"/>
       <c r="L27" s="11" t="s">
         <v>29</v>
       </c>
@@ -2955,9 +2952,9 @@
       <c r="N27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="31"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="31"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="26"/>
       <c r="R27" s="11" t="s">
         <v>29</v>
       </c>
@@ -2967,16 +2964,16 @@
       <c r="T27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U27" s="31"/>
+      <c r="U27" s="26"/>
       <c r="V27" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W27" s="5">
-        <f>COUNTIF(F27:V27,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X27" s="5">
-        <f>COUNTIF(F27:V27,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2997,31 +2994,39 @@
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
-      <c r="I28" s="34"/>
+      <c r="I28" s="24"/>
       <c r="J28" s="11"/>
-      <c r="K28" s="31"/>
+      <c r="K28" s="26"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="31"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="26"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
-      <c r="U28" s="31"/>
+      <c r="U28" s="26"/>
       <c r="V28" s="11"/>
       <c r="W28" s="5">
-        <f>COUNTIF(F28:V28,"P")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X28" s="5">
-        <f>COUNTIF(F28:V28,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
     <mergeCell ref="I5:I28"/>
@@ -3032,64 +3037,56 @@
     <mergeCell ref="U5:U28"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y4:Z4 J6:J28 L6:N28 F5:Q5 V5:V28 U5 R5:T28 F6:H28 F3:V4">
-    <cfRule type="expression" dxfId="16" priority="15">
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T28 V5:V28 F6:H28 J6:J28 L6:N28 F4:V4">
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T28 V5:V28 F6:H28 J6:J28 L6:N28">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:V4 F5:Q5 U5 R5:T28 V5:V28 F6:H28 J6:J28 L6:N28 Y4:Z4">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J28 L6:N28 F5:Q5 V5:V28 U5 R5:T28 F6:H28 F4:V4">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="W3:X3 W5:X28">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="11" priority="16">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y5:Y6">
-    <cfRule type="expression" dxfId="13" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y9:Y12">
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y17:Y20">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z9:AB9">
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>Z$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z17:AB17">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>Z$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J28 L6:N28 F5:Q5 V5:V28 U5 R5:T28 F6:H28">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3102,7 +3099,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3132,206 +3129,321 @@
     <col min="29" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="22"/>
+    <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>23</v>
+      </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
-    </row>
-    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+    </row>
+    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
       <c r="E2" s="23"/>
-    </row>
-    <row r="3" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+    </row>
+    <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <f t="shared" ref="F4:V4" si="0">TEXT(F5,"ddd")</f>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:V3" si="0">TEXT(F4,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="G4" s="2" t="str">
+      <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="I4" s="2" t="str">
+      <c r="I3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="K4" s="2" t="str">
+      <c r="K3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="L4" s="2" t="str">
+      <c r="L3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="M4" s="2" t="str">
+      <c r="M3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="N4" s="2" t="str">
+      <c r="N3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="O4" s="2" t="str">
+      <c r="O3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="P4" s="2" t="str">
+      <c r="P3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="Q4" s="2" t="str">
+      <c r="Q3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="R4" s="2" t="str">
+      <c r="R3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="S4" s="2" t="str">
+      <c r="S3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="T4" s="2" t="str">
+      <c r="T3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="U4" s="2" t="str">
+      <c r="U3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="V4" s="2" t="str">
+      <c r="V3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W4" s="33" t="s">
+      <c r="W3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="33" t="s">
+      <c r="X3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="25" t="s">
+      <c r="Y3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="27"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="21">
+        <v>45519</v>
+      </c>
+      <c r="G4" s="21">
+        <v>45520</v>
+      </c>
+      <c r="H4" s="21">
+        <v>45521</v>
+      </c>
+      <c r="I4" s="21">
+        <v>45522</v>
+      </c>
+      <c r="J4" s="21">
+        <v>45523</v>
+      </c>
+      <c r="K4" s="21">
+        <v>45524</v>
+      </c>
+      <c r="L4" s="21">
+        <v>45525</v>
+      </c>
+      <c r="M4" s="21">
+        <v>45526</v>
+      </c>
+      <c r="N4" s="21">
+        <v>45527</v>
+      </c>
+      <c r="O4" s="21">
+        <v>45528</v>
+      </c>
+      <c r="P4" s="21">
+        <v>45529</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>45530</v>
+      </c>
+      <c r="R4" s="21">
+        <v>45531</v>
+      </c>
+      <c r="S4" s="21">
+        <v>45532</v>
+      </c>
+      <c r="T4" s="21">
+        <v>45533</v>
+      </c>
+      <c r="U4" s="21">
+        <v>45534</v>
+      </c>
+      <c r="V4" s="21">
+        <v>45535</v>
+      </c>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>31</v>
+      </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
     </row>
-    <row r="5" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="21">
-        <v>45519</v>
-      </c>
-      <c r="G5" s="21">
-        <v>45520</v>
-      </c>
-      <c r="H5" s="21">
-        <v>45521</v>
-      </c>
-      <c r="I5" s="21">
-        <v>45522</v>
-      </c>
-      <c r="J5" s="21">
-        <v>45523</v>
-      </c>
-      <c r="K5" s="21">
-        <v>45524</v>
-      </c>
-      <c r="L5" s="21">
-        <v>45525</v>
-      </c>
-      <c r="M5" s="21">
-        <v>45526</v>
-      </c>
-      <c r="N5" s="21">
-        <v>45527</v>
-      </c>
-      <c r="O5" s="21">
-        <v>45528</v>
-      </c>
-      <c r="P5" s="21">
-        <v>45529</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>45530</v>
-      </c>
-      <c r="R5" s="21">
-        <v>45531</v>
-      </c>
-      <c r="S5" s="21">
-        <v>45532</v>
-      </c>
-      <c r="T5" s="21">
-        <v>45533</v>
-      </c>
-      <c r="U5" s="21">
-        <v>45534</v>
-      </c>
-      <c r="V5" s="21">
-        <v>45535</v>
-      </c>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="4" t="s">
+    <row r="5" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="5">
+        <f t="shared" ref="W5:W36" si="1">COUNTIF(F5:V5,"P")</f>
         <v>7</v>
       </c>
-      <c r="Z5" s="5">
-        <v>31</v>
-      </c>
-      <c r="AA5" s="3"/>
+      <c r="X5" s="5">
+        <f t="shared" ref="X5:X36" si="2">COUNTIF(F5:V5,"A")</f>
+        <v>4</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="12">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7"/>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>76</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>20</v>
@@ -3345,15 +3457,11 @@
       <c r="H6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="34" t="s">
-        <v>131</v>
-      </c>
+      <c r="I6" s="24"/>
       <c r="J6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="30" t="s">
-        <v>129</v>
-      </c>
+      <c r="K6" s="26"/>
       <c r="L6" s="11" t="s">
         <v>29</v>
       </c>
@@ -3363,59 +3471,49 @@
       <c r="N6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>134</v>
-      </c>
+      <c r="O6" s="26"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="26"/>
       <c r="R6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="30" t="s">
-        <v>130</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="U6" s="26"/>
       <c r="V6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W6" s="5">
-        <f>COUNTIF(F6:V6,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="X6" s="5">
-        <f>COUNTIF(F6:V6,"A")</f>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="12">
         <v>4</v>
       </c>
-      <c r="Y6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z6" s="12">
-        <v>26</v>
-      </c>
-      <c r="AA6" s="13" t="s">
-        <v>9</v>
-      </c>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
-        <v>2</v>
+      <c r="A7" s="6">
+        <v>3</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
@@ -3429,11 +3527,11 @@
       <c r="H7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="34"/>
+      <c r="I7" s="24"/>
       <c r="J7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="26"/>
       <c r="L7" s="11" t="s">
         <v>29</v>
       </c>
@@ -3443,49 +3541,45 @@
       <c r="N7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="31"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="26"/>
       <c r="R7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U7" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U7" s="26"/>
       <c r="V7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W7" s="5">
-        <f>COUNTIF(F7:V7,"P")</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X7" s="5">
-        <f>COUNTIF(F7:V7,"A")</f>
-        <v>6</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z7" s="12">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>3</v>
+    <row r="8" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>4</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -3499,11 +3593,11 @@
       <c r="H8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="34"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="26"/>
       <c r="L8" s="11" t="s">
         <v>29</v>
       </c>
@@ -3513,63 +3607,65 @@
       <c r="N8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="31"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="26"/>
       <c r="R8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S8" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U8" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U8" s="26"/>
       <c r="V8" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W8" s="5">
-        <f>COUNTIF(F8:V8,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="X8" s="5">
-        <f>COUNTIF(F8:V8,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-    </row>
-    <row r="9" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="Y8" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>5</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>28</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="I9" s="24"/>
       <c r="J9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="26"/>
       <c r="L9" s="11" t="s">
         <v>29</v>
       </c>
@@ -3579,47 +3675,53 @@
       <c r="N9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="31"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="31"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="26"/>
       <c r="R9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U9" s="31"/>
+      <c r="U9" s="26"/>
       <c r="V9" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W9" s="5">
-        <f>COUNTIF(F9:V9,"P")</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X9" s="5">
-        <f>COUNTIF(F9:V9,"A")</f>
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
         <v>6</v>
-      </c>
-      <c r="Y9" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="26"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>5</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>20</v>
@@ -3628,16 +3730,16 @@
         <v>29</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="34"/>
+        <v>29</v>
+      </c>
+      <c r="I10" s="24"/>
       <c r="J10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="31"/>
+      <c r="K10" s="26"/>
       <c r="L10" s="11" t="s">
         <v>29</v>
       </c>
@@ -3647,53 +3749,56 @@
       <c r="N10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="31"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="26"/>
       <c r="R10" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U10" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U10" s="26"/>
       <c r="V10" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W10" s="5">
-        <f>COUNTIF(F10:V10,"P")</f>
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="X10" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>19*26</f>
+        <v>494</v>
+      </c>
+      <c r="AA10" s="12">
+        <f>21*26</f>
+        <v>546</v>
+      </c>
+      <c r="AB10" s="12">
+        <f>SUM(Z10:AA10)</f>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>7</v>
-      </c>
-      <c r="X10" s="5">
-        <f>COUNTIF(F10:V10,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>6</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>20</v>
@@ -3702,16 +3807,16 @@
         <v>29</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="I11" s="24"/>
       <c r="J11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="K11" s="26"/>
       <c r="L11" s="11" t="s">
         <v>29</v>
       </c>
@@ -3721,56 +3826,56 @@
       <c r="N11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="31"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="31"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="26"/>
       <c r="R11" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S11" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U11" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U11" s="26"/>
       <c r="V11" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W11" s="5">
-        <f>COUNTIF(F11:V11,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="X11" s="5">
-        <f>COUNTIF(F11:V11,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="Y11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z11" s="12">
+        <f>+W7+W18</f>
         <v>16</v>
       </c>
-      <c r="Z11" s="12">
-        <f>19*26</f>
-        <v>494</v>
-      </c>
       <c r="AA11" s="12">
-        <f>21*26</f>
-        <v>546</v>
+        <f>W5+W6+W8+W9+W10+W11+W12+W13+W14+W15+W16+W17+W19+W20</f>
+        <v>96</v>
       </c>
       <c r="AB11" s="12">
-        <f>SUM(Z11:AA11)</f>
-        <v>1040</v>
+        <f>Z11+AA11</f>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>7</v>
+      <c r="A12" s="12">
+        <v>8</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
@@ -3779,28 +3884,28 @@
         <v>29</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="34"/>
+        <v>29</v>
+      </c>
+      <c r="I12" s="24"/>
       <c r="J12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="K12" s="26"/>
       <c r="L12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="31"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="31"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="26"/>
       <c r="R12" s="11" t="s">
         <v>28</v>
       </c>
@@ -3808,46 +3913,46 @@
         <v>28</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U12" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U12" s="26"/>
       <c r="V12" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W12" s="5">
-        <f>COUNTIF(F12:V12,"P")</f>
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="X12" s="5">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="X12" s="5">
-        <f>COUNTIF(F12:V12,"A")</f>
-        <v>7</v>
-      </c>
       <c r="Y12" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z12" s="12">
-        <f>+W8+W19</f>
-        <v>16</v>
+        <f>Z11/Z10</f>
+        <v>3.2388663967611336E-2</v>
       </c>
       <c r="AA12" s="12">
-        <f>W6+W7+W9+W10+W11+W12+W13+W14+W15+W16+W17+W18+W20+W21</f>
-        <v>96</v>
+        <f>AA11/AA10</f>
+        <v>0.17582417582417584</v>
       </c>
       <c r="AB12" s="12">
-        <f>Z12+AA12</f>
-        <v>112</v>
+        <f>AB11/AB10</f>
+        <v>0.1076923076923077</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>8</v>
+      <c r="A13" s="6">
+        <v>9</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="15" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>20</v>
@@ -3861,25 +3966,25 @@
       <c r="H13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="34"/>
+      <c r="I13" s="24"/>
       <c r="J13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="31"/>
+      <c r="K13" s="26"/>
       <c r="L13" s="11" t="s">
         <v>29</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="31"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="26"/>
       <c r="R13" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S13" s="11" t="s">
         <v>28</v>
@@ -3887,50 +3992,39 @@
       <c r="T13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U13" s="31"/>
+      <c r="U13" s="26"/>
       <c r="V13" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W13" s="5">
-        <f>COUNTIF(F13:V13,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X13" s="5">
-        <f>COUNTIF(F13:V13,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="Y13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z13" s="12">
-        <f>Z12/Z11</f>
-        <v>3.2388663967611336E-2</v>
-      </c>
-      <c r="AA13" s="12">
-        <f>AA12/AA11</f>
-        <v>0.17582417582417584</v>
-      </c>
-      <c r="AB13" s="12">
-        <f>AB12/AB11</f>
-        <v>0.1076923076923077</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>9</v>
+      <c r="A14" s="12">
+        <v>10</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="15" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>29</v>
@@ -3938,11 +4032,11 @@
       <c r="H14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="34"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="31"/>
+      <c r="K14" s="26"/>
       <c r="L14" s="11" t="s">
         <v>29</v>
       </c>
@@ -3952,63 +4046,63 @@
       <c r="N14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="31"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="31"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="26"/>
       <c r="R14" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U14" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U14" s="26"/>
       <c r="V14" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W14" s="5">
-        <f>COUNTIF(F14:V14,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X14" s="5">
-        <f>COUNTIF(F14:V14,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>10</v>
+      <c r="A15" s="6">
+        <v>11</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="I15" s="24"/>
       <c r="J15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="31"/>
+      <c r="K15" s="26"/>
       <c r="L15" s="11" t="s">
         <v>29</v>
       </c>
@@ -4018,45 +4112,45 @@
       <c r="N15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="31"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="26"/>
       <c r="R15" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U15" s="31"/>
+      <c r="U15" s="26"/>
       <c r="V15" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W15" s="5">
-        <f>COUNTIF(F15:V15,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="X15" s="5">
-        <f>COUNTIF(F15:V15,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+    </row>
+    <row r="16" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>12</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>20</v>
@@ -4068,13 +4162,13 @@
         <v>29</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="34"/>
+        <v>29</v>
+      </c>
+      <c r="I16" s="24"/>
       <c r="J16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="26"/>
       <c r="L16" s="11" t="s">
         <v>29</v>
       </c>
@@ -4084,51 +4178,53 @@
       <c r="N16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O16" s="31"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="31"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="26"/>
       <c r="R16" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U16" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U16" s="26"/>
       <c r="V16" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W16" s="5">
-        <f>COUNTIF(F16:V16,"P")</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="X16" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Y16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="X16" s="5">
-        <f>COUNTIF(F16:V16,"A")</f>
-        <v>5</v>
-      </c>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>12</v>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="30"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>13</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="15" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>29</v>
@@ -4136,11 +4232,11 @@
       <c r="H17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="34"/>
+      <c r="I17" s="24"/>
       <c r="J17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="26"/>
       <c r="L17" s="11" t="s">
         <v>29</v>
       </c>
@@ -4150,53 +4246,59 @@
       <c r="N17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="31"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="31"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="26"/>
       <c r="R17" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U17" s="31"/>
+      <c r="U17" s="26"/>
       <c r="V17" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W17" s="5">
-        <f>COUNTIF(F17:V17,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X17" s="5">
-        <f>COUNTIF(F17:V17,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="Y17" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="26"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>13</v>
+      <c r="A18" s="12">
+        <v>14</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>29</v>
@@ -4204,11 +4306,11 @@
       <c r="H18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="34"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="26"/>
       <c r="L18" s="11" t="s">
         <v>29</v>
       </c>
@@ -4218,9 +4320,9 @@
       <c r="N18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="31"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="31"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="26"/>
       <c r="R18" s="11" t="s">
         <v>29</v>
       </c>
@@ -4230,59 +4332,62 @@
       <c r="T18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U18" s="31"/>
+      <c r="U18" s="26"/>
       <c r="V18" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W18" s="5">
-        <f>COUNTIF(F18:V18,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X18" s="5">
-        <f>COUNTIF(F18:V18,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="Y18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z18" s="12">
+        <f>19*26</f>
+        <v>494</v>
+      </c>
+      <c r="AA18" s="12">
+        <f>21*26</f>
+        <v>546</v>
+      </c>
+      <c r="AB18" s="12">
+        <f>Z18+AA18</f>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>14</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="15" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="I19" s="24"/>
       <c r="J19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="31"/>
+      <c r="K19" s="26"/>
       <c r="L19" s="11" t="s">
         <v>29</v>
       </c>
@@ -4292,9 +4397,9 @@
       <c r="N19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="31"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="31"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="26"/>
       <c r="R19" s="11" t="s">
         <v>29</v>
       </c>
@@ -4302,46 +4407,46 @@
         <v>28</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U19" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U19" s="26"/>
       <c r="V19" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W19" s="5">
-        <f>COUNTIF(F19:V19,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="X19" s="5">
-        <f>COUNTIF(F19:V19,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="Y19" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="12">
-        <f>19*26</f>
-        <v>494</v>
+        <f>Z18-Z11</f>
+        <v>478</v>
       </c>
       <c r="AA19" s="12">
-        <f>21*26</f>
-        <v>546</v>
+        <f>AA18-AA11</f>
+        <v>450</v>
       </c>
       <c r="AB19" s="12">
         <f>Z19+AA19</f>
-        <v>1040</v>
+        <v>928</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>15</v>
+      <c r="A20" s="12">
+        <v>16</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>20</v>
@@ -4350,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="34"/>
+        <v>29</v>
+      </c>
+      <c r="I20" s="24"/>
       <c r="J20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="26"/>
       <c r="L20" s="11" t="s">
         <v>29</v>
       </c>
@@ -4369,11 +4474,11 @@
       <c r="N20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="31"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="31"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="26"/>
       <c r="R20" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S20" s="11" t="s">
         <v>28</v>
@@ -4381,62 +4486,62 @@
       <c r="T20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U20" s="31"/>
+      <c r="U20" s="26"/>
       <c r="V20" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W20" s="5">
-        <f>COUNTIF(F20:V20,"P")</f>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="X20" s="5">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="X20" s="5">
-        <f>COUNTIF(F20:V20,"A")</f>
-        <v>5</v>
-      </c>
       <c r="Y20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z20" s="12">
-        <f>Z19-Z12</f>
-        <v>478</v>
-      </c>
-      <c r="AA20" s="12">
-        <f>AA19-AA12</f>
-        <v>450</v>
-      </c>
-      <c r="AB20" s="12">
-        <f>Z20+AA20</f>
-        <v>928</v>
+        <v>15</v>
+      </c>
+      <c r="Z20" s="20">
+        <f>Z19/Z18</f>
+        <v>0.96761133603238869</v>
+      </c>
+      <c r="AA20" s="20">
+        <f>AA19/AA18</f>
+        <v>0.82417582417582413</v>
+      </c>
+      <c r="AB20" s="20">
+        <f>AB19/AB18</f>
+        <v>0.89230769230769236</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>16</v>
+      <c r="A21" s="6">
+        <v>17</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I21" s="34"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="26"/>
       <c r="L21" s="11" t="s">
         <v>29</v>
       </c>
@@ -4444,11 +4549,11 @@
         <v>29</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="31"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="O21" s="26"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="26"/>
       <c r="R21" s="11" t="s">
         <v>28</v>
       </c>
@@ -4456,46 +4561,31 @@
         <v>28</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U21" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U21" s="26"/>
       <c r="V21" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W21" s="5">
-        <f>COUNTIF(F21:V21,"P")</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X21" s="5">
-        <f>COUNTIF(F21:V21,"A")</f>
-        <v>6</v>
-      </c>
-      <c r="Y21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z21" s="20">
-        <f>Z20/Z19</f>
-        <v>0.96761133603238869</v>
-      </c>
-      <c r="AA21" s="20">
-        <f>AA20/AA19</f>
-        <v>0.82417582417582413</v>
-      </c>
-      <c r="AB21" s="20">
-        <f>AB20/AB19</f>
-        <v>0.89230769230769236</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>17</v>
+      <c r="A22" s="12">
+        <v>18</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>20</v>
@@ -4509,11 +4599,11 @@
       <c r="H22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="34"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="26"/>
       <c r="L22" s="11" t="s">
         <v>29</v>
       </c>
@@ -4521,13 +4611,13 @@
         <v>29</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="31"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="O22" s="26"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="26"/>
       <c r="R22" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>28</v>
@@ -4535,29 +4625,29 @@
       <c r="T22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U22" s="31"/>
+      <c r="U22" s="26"/>
       <c r="V22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W22" s="5">
-        <f>COUNTIF(F22:V22,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X22" s="5">
-        <f>COUNTIF(F22:V22,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>18</v>
+      <c r="A23" s="6">
+        <v>19</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>20</v>
@@ -4571,11 +4661,11 @@
       <c r="H23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="34"/>
+      <c r="I23" s="24"/>
       <c r="J23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="31"/>
+      <c r="K23" s="26"/>
       <c r="L23" s="11" t="s">
         <v>29</v>
       </c>
@@ -4585,11 +4675,11 @@
       <c r="N23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="31"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="31"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="26"/>
       <c r="R23" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>28</v>
@@ -4597,29 +4687,29 @@
       <c r="T23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U23" s="31"/>
+      <c r="U23" s="26"/>
       <c r="V23" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W23" s="5">
-        <f>COUNTIF(F23:V23,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X23" s="5">
-        <f>COUNTIF(F23:V23,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>19</v>
+      <c r="A24" s="12">
+        <v>20</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>20</v>
@@ -4633,11 +4723,11 @@
       <c r="H24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="34"/>
+      <c r="I24" s="24"/>
       <c r="J24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="26"/>
       <c r="L24" s="11" t="s">
         <v>29</v>
       </c>
@@ -4647,41 +4737,41 @@
       <c r="N24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="31"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="31"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="26"/>
       <c r="R24" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U24" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U24" s="26"/>
       <c r="V24" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W24" s="5">
-        <f>COUNTIF(F24:V24,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X24" s="5">
-        <f>COUNTIF(F24:V24,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>20</v>
+      <c r="A25" s="6">
+        <v>21</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>20</v>
@@ -4695,11 +4785,11 @@
       <c r="H25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="34"/>
+      <c r="I25" s="24"/>
       <c r="J25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="26"/>
       <c r="L25" s="11" t="s">
         <v>29</v>
       </c>
@@ -4709,11 +4799,11 @@
       <c r="N25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O25" s="31"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="31"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="26"/>
       <c r="R25" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>28</v>
@@ -4721,29 +4811,29 @@
       <c r="T25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U25" s="31"/>
+      <c r="U25" s="26"/>
       <c r="V25" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W25" s="5">
-        <f>COUNTIF(F25:V25,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X25" s="5">
-        <f>COUNTIF(F25:V25,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>21</v>
+      <c r="A26" s="12">
+        <v>22</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>20</v>
@@ -4757,11 +4847,11 @@
       <c r="H26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="34"/>
+      <c r="I26" s="24"/>
       <c r="J26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K26" s="31"/>
+      <c r="K26" s="26"/>
       <c r="L26" s="11" t="s">
         <v>29</v>
       </c>
@@ -4769,49 +4859,49 @@
         <v>29</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O26" s="31"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="O26" s="26"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="26"/>
       <c r="R26" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U26" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U26" s="26"/>
       <c r="V26" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W26" s="5">
-        <f>COUNTIF(F26:V26,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X26" s="5">
-        <f>COUNTIF(F26:V26,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>22</v>
+      <c r="A27" s="6">
+        <v>23</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>29</v>
@@ -4819,11 +4909,11 @@
       <c r="H27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="34"/>
+      <c r="I27" s="24"/>
       <c r="J27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="31"/>
+      <c r="K27" s="26"/>
       <c r="L27" s="11" t="s">
         <v>29</v>
       </c>
@@ -4831,43 +4921,43 @@
         <v>29</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" s="31"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="O27" s="26"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="26"/>
       <c r="R27" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U27" s="31"/>
+      <c r="U27" s="26"/>
       <c r="V27" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W27" s="5">
-        <f>COUNTIF(F27:V27,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X27" s="5">
-        <f>COUNTIF(F27:V27,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>23</v>
+      <c r="A28" s="12">
+        <v>24</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>20</v>
@@ -4881,11 +4971,11 @@
       <c r="H28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="34"/>
+      <c r="I28" s="24"/>
       <c r="J28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K28" s="31"/>
+      <c r="K28" s="26"/>
       <c r="L28" s="11" t="s">
         <v>29</v>
       </c>
@@ -4895,47 +4985,47 @@
       <c r="N28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="31"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="31"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="26"/>
       <c r="R28" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="U28" s="31"/>
+      <c r="U28" s="26"/>
       <c r="V28" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W28" s="5">
-        <f>COUNTIF(F28:V28,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X28" s="5">
-        <f>COUNTIF(F28:V28,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>24</v>
+      <c r="A29" s="6">
+        <v>25</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="15" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>29</v>
@@ -4943,11 +5033,11 @@
       <c r="H29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="34"/>
+      <c r="I29" s="24"/>
       <c r="J29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K29" s="31"/>
+      <c r="K29" s="26"/>
       <c r="L29" s="11" t="s">
         <v>29</v>
       </c>
@@ -4957,47 +5047,47 @@
       <c r="N29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O29" s="31"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="31"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="26"/>
       <c r="R29" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U29" s="26"/>
       <c r="V29" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W29" s="5">
-        <f>COUNTIF(F29:V29,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X29" s="5">
-        <f>COUNTIF(F29:V29,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>25</v>
+      <c r="A30" s="12">
+        <v>26</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>29</v>
@@ -5005,11 +5095,11 @@
       <c r="H30" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I30" s="34"/>
+      <c r="I30" s="24"/>
       <c r="J30" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K30" s="31"/>
+      <c r="K30" s="26"/>
       <c r="L30" s="11" t="s">
         <v>29</v>
       </c>
@@ -5017,11 +5107,11 @@
         <v>29</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="31"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="O30" s="26"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="26"/>
       <c r="R30" s="11" t="s">
         <v>28</v>
       </c>
@@ -5031,29 +5121,29 @@
       <c r="T30" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U30" s="31"/>
+      <c r="U30" s="26"/>
       <c r="V30" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W30" s="5">
-        <f>COUNTIF(F30:V30,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="X30" s="5">
-        <f>COUNTIF(F30:V30,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
-        <v>26</v>
+      <c r="A31" s="6">
+        <v>27</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="15" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>20</v>
@@ -5067,11 +5157,11 @@
       <c r="H31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="34"/>
+      <c r="I31" s="24"/>
       <c r="J31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K31" s="31"/>
+      <c r="K31" s="26"/>
       <c r="L31" s="11" t="s">
         <v>29</v>
       </c>
@@ -5079,11 +5169,11 @@
         <v>29</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O31" s="31"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="O31" s="26"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="26"/>
       <c r="R31" s="11" t="s">
         <v>28</v>
       </c>
@@ -5091,145 +5181,145 @@
         <v>28</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U31" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U31" s="26"/>
       <c r="V31" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W31" s="5">
-        <f>COUNTIF(F31:V31,"P")</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X31" s="5">
-        <f>COUNTIF(F31:V31,"A")</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>27</v>
+      <c r="A32" s="12">
+        <v>28</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="15" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I32" s="34"/>
-      <c r="J32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="11" t="s">
-        <v>29</v>
-      </c>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="11"/>
       <c r="M32" s="11" t="s">
         <v>29</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" s="31"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="O32" s="26"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="26"/>
       <c r="R32" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>28</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U32" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U32" s="26"/>
       <c r="V32" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W32" s="5">
-        <f>COUNTIF(F32:V32,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="X32" s="5">
-        <f>COUNTIF(F32:V32,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
-        <v>28</v>
+      <c r="A33" s="6">
+        <v>29</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="26"/>
+      <c r="L33" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="M33" s="11" t="s">
         <v>29</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O33" s="31"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="O33" s="26"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="26"/>
       <c r="R33" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U33" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U33" s="26"/>
       <c r="V33" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W33" s="5">
-        <f>COUNTIF(F33:V33,"P")</f>
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="X33" s="5">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="X33" s="5">
-        <f>COUNTIF(F33:V33,"A")</f>
-        <v>4</v>
-      </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>29</v>
+      <c r="A34" s="12">
+        <v>30</v>
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>20</v>
@@ -5243,11 +5333,11 @@
       <c r="H34" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I34" s="34"/>
+      <c r="I34" s="24"/>
       <c r="J34" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K34" s="31"/>
+      <c r="K34" s="26"/>
       <c r="L34" s="11" t="s">
         <v>29</v>
       </c>
@@ -5257,47 +5347,47 @@
       <c r="N34" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O34" s="31"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="31"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="26"/>
       <c r="R34" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S34" s="11" t="s">
         <v>29</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U34" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U34" s="26"/>
       <c r="V34" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W34" s="5">
-        <f>COUNTIF(F34:V34,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X34" s="5">
-        <f>COUNTIF(F34:V34,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>30</v>
+      <c r="A35" s="6">
+        <v>31</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="15" t="s">
         <v>124</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>29</v>
@@ -5305,11 +5395,11 @@
       <c r="H35" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="34"/>
+      <c r="I35" s="24"/>
       <c r="J35" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="31"/>
+      <c r="K35" s="26"/>
       <c r="L35" s="11" t="s">
         <v>29</v>
       </c>
@@ -5319,41 +5409,41 @@
       <c r="N35" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O35" s="31"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="31"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="26"/>
       <c r="R35" s="11" t="s">
         <v>29</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U35" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="U35" s="26"/>
       <c r="V35" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W35" s="5">
-        <f>COUNTIF(F35:V35,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X35" s="5">
-        <f>COUNTIF(F35:V35,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>31</v>
+      <c r="A36" s="12">
+        <v>32</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>20</v>
@@ -5365,13 +5455,13 @@
         <v>29</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I36" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="I36" s="24"/>
       <c r="J36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K36" s="31"/>
+      <c r="K36" s="33"/>
       <c r="L36" s="11" t="s">
         <v>29</v>
       </c>
@@ -5381,9 +5471,9 @@
       <c r="N36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O36" s="31"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="31"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="33"/>
       <c r="R36" s="11" t="s">
         <v>29</v>
       </c>
@@ -5391,129 +5481,66 @@
         <v>28</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="U36" s="31"/>
+        <v>28</v>
+      </c>
+      <c r="U36" s="33"/>
       <c r="V36" s="11" t="s">
         <v>28</v>
       </c>
       <c r="W36" s="5">
-        <f>COUNTIF(F36:V36,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="X36" s="5">
-        <f>COUNTIF(F36:V36,"A")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>32</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="34"/>
-      <c r="J37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="32"/>
-      <c r="L37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="32"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="32"/>
-      <c r="R37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="S37" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="T37" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="U37" s="32"/>
-      <c r="V37" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="W37" s="5">
-        <f>COUNTIF(F37:V37,"P")</f>
-        <v>6</v>
-      </c>
-      <c r="X37" s="5">
-        <f>COUNTIF(F37:V37,"A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="Y17:AB17"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="I6:I37"/>
-    <mergeCell ref="K6:K37"/>
-    <mergeCell ref="O6:O37"/>
-    <mergeCell ref="P6:P37"/>
-    <mergeCell ref="Q6:Q37"/>
-    <mergeCell ref="U6:U37"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
+  <mergeCells count="18">
+    <mergeCell ref="U5:U36"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="I5:I36"/>
+    <mergeCell ref="K5:K36"/>
+    <mergeCell ref="O5:O36"/>
+    <mergeCell ref="P5:P36"/>
+    <mergeCell ref="Q5:Q36"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Z3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J7:J37 L7:N37 V6:V37 R6:T37 F6:H37 F6:U6 Y5:Z5 Y6:Y7 Y10:Y13 Y18:Y21 Z10:AB10 Z18:AB18 F4:V5">
-    <cfRule type="expression" dxfId="5" priority="10">
-      <formula>F$4="Sun"</formula>
+  <conditionalFormatting sqref="F5:U5 F5:H36 R5:T36 V5:V36 J6:J36 L6:N36 F4:V4">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J37 L7:N37 V6:V37 R6:T37 F6:H37 F6:U6 F5:V5">
-    <cfRule type="expression" dxfId="4" priority="9">
-      <formula>IF(F$5=TODAY(),TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="F5:U5 F5:H36 R5:T36 V5:V36 J6:J36 L6:N36">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W4:X4 W6:X37">
-    <cfRule type="expression" dxfId="3" priority="11">
-      <formula>#REF!="Sun"</formula>
+  <conditionalFormatting sqref="F3:V4 F5:U5 F5:H36 R5:T36 V5:V36 J6:J36 L6:N36 Y4:Z4 Y5:Y6 Z9:AB9 Y9:Y12 Z17:AB17 Y17:Y20">
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J37 L7:N37 V6:V37 R6:T37 F6:H37 F6:U6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"P"</formula>
+  <conditionalFormatting sqref="W3:X3 W5:X36">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
